--- a/vocab jlpt N3 record.xlsx
+++ b/vocab jlpt N3 record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gideo\Desktop\MAIN FOR KANJI\KANJIPRACTICE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89D3B99-A900-4FE8-AC3E-5277F9CA9543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6E586D-5B9A-4C11-9663-648BC99B6FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21465" yWindow="0" windowWidth="7440" windowHeight="7845" xr2:uid="{C1F780F9-615F-4565-A6FA-57151FF7223D}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{C1F780F9-615F-4565-A6FA-57151FF7223D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Date</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>１４１１</t>
+  </si>
+  <si>
+    <t>2.5 hrs</t>
+  </si>
+  <si>
+    <t>1.2 hrs</t>
+  </si>
+  <si>
+    <t>2 hrs</t>
   </si>
 </sst>
 </file>
@@ -523,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C41" si="0">$E$2+(50*B3)</f>
+        <f t="shared" ref="C3:C39" si="0">$E$2+(50*B3)</f>
         <v>1300</v>
       </c>
       <c r="D3" s="4">
@@ -994,14 +1003,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46104</v>
+        <v>46098</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <f>$E$42+(50*B2)</f>
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -1009,185 +1017,153 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46105</v>
+        <v>46099</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43">
-        <f t="shared" ref="C43:C57" si="1">$E$42+(50*B3)</f>
-        <v>100</v>
+        <v>350</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44">
-        <f t="shared" si="1"/>
-        <v>150</v>
+        <v>440</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <v>550</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>46108</v>
+        <v>46102</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
-      <c r="C46">
-        <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46109</v>
+        <v>46103</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
-      <c r="C47">
-        <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>46110</v>
+        <v>46104</v>
       </c>
       <c r="B48">
         <v>7</v>
       </c>
-      <c r="C48">
-        <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46111</v>
+        <v>46105</v>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
-      <c r="C49">
-        <f t="shared" si="1"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="B50">
         <v>9</v>
       </c>
-      <c r="C50">
-        <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B51">
         <v>10</v>
       </c>
-      <c r="C51">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46114</v>
+        <v>46108</v>
       </c>
       <c r="B52">
         <v>11</v>
       </c>
-      <c r="C52">
-        <f t="shared" si="1"/>
-        <v>550</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>46115</v>
+        <v>46109</v>
       </c>
       <c r="B53">
         <v>12</v>
       </c>
-      <c r="C53">
-        <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>46116</v>
+        <v>46110</v>
       </c>
       <c r="B54">
         <v>13</v>
       </c>
-      <c r="C54">
-        <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>46117</v>
+        <v>46111</v>
       </c>
       <c r="B55">
         <v>14</v>
       </c>
-      <c r="C55">
-        <f t="shared" si="1"/>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
